--- a/data/data_monitoreo_19_de_agosto.xlsx
+++ b/data/data_monitoreo_19_de_agosto.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>199</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
@@ -457,87 +457,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>179</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TENE TRABUCCO GIAN PIERRE</t>
+          <t>AGURTO TINEO CESIA JIMENA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AGURTO TINEO CESIA JIMENA</t>
+          <t>TUANAMA PIZANGO ELIZABETH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>157</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TUANAMA PIZANGO ELIZABETH</t>
+          <t>TENE TRABUCCO GIAN PIERRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHIROQUE YARLEQUE BETTY ELIZABETH</t>
+          <t>SILVA ALVARADO EVELYN DE JESUS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MORETO ESPINOZA CRISTIAN ESTEBAN</t>
+          <t>CHIROQUE YARLEQUE BETTY ELIZABETH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SANCARRANCO SANCHEZ DE CRUZ GISSELA SHANI</t>
+          <t>MORETO ESPINOZA CRISTIAN ESTEBAN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HERRERA JUAN MANUEL</t>
+          <t>SANCARRANCO SANCHEZ DE CRUZ GISSELA SHANI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SILVA ALVARADO EVELYN DE JESUS</t>
+          <t>HERRERA JUAN MANUEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_19_de_agosto.xlsx
+++ b/data/data_monitoreo_19_de_agosto.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
@@ -457,57 +457,57 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AGURTO TINEO CESIA JIMENA</t>
+          <t>TUANAMA PIZANGO ELIZABETH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TUANAMA PIZANGO ELIZABETH</t>
+          <t>TENE TRABUCCO GIAN PIERRE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TENE TRABUCCO GIAN PIERRE</t>
+          <t>AGURTO TINEO CESIA JIMENA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SILVA ALVARADO EVELYN DE JESUS</t>
+          <t>CHIROQUE YARLEQUE BETTY ELIZABETH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHIROQUE YARLEQUE BETTY ELIZABETH</t>
+          <t>SILVA ALVARADO EVELYN DE JESUS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_19_de_agosto.xlsx
+++ b/data/data_monitoreo_19_de_agosto.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3">
@@ -457,17 +457,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TUANAMA PIZANGO ELIZABETH</t>
+          <t>AGURTO TINEO CESIA JIMENA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -477,17 +477,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AGURTO TINEO CESIA JIMENA</t>
+          <t>TUANAMA PIZANGO ELIZABETH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_19_de_agosto.xlsx
+++ b/data/data_monitoreo_19_de_agosto.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>301</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TENE TRABUCCO GIAN PIERRE</t>
+          <t>TUANAMA PIZANGO ELIZABETH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>268</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TUANAMA PIZANGO ELIZABETH</t>
+          <t>TENE TRABUCCO GIAN PIERRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>230</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>226</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_19_de_agosto.xlsx
+++ b/data/data_monitoreo_19_de_agosto.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>416</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
